--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_205_R21.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_205_R21.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.6692</v>
+        <v>9.6341</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6228</v>
+        <v>7.8901</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0464</v>
+        <v>1.744</v>
       </c>
       <c r="G2" t="n">
         <v>8.356400000000001</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0655</v>
+        <v>0.0303</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8804</v>
+        <v>-0.613</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9458</v>
+        <v>0.6434</v>
       </c>
       <c r="V2" t="n">
         <v>-1.0722</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.146</v>
+        <v>4.4133</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5036</v>
+        <v>2.771</v>
       </c>
       <c r="F3" t="n">
         <v>1.6423</v>
@@ -688,10 +688,10 @@
         <v>3.4793</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9619</v>
+        <v>-1.6946</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.6798</v>
       </c>
       <c r="U3" t="n">
         <v>-1.0148</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>E. BRYANT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0351</v>
+        <v>3.2061</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2696</v>
+        <v>2.6498</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7655</v>
+        <v>0.5563</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5174</v>
+        <v>5.0661</v>
       </c>
       <c r="H4" t="n">
-        <v>3.347</v>
+        <v>2.6469</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8297</v>
+        <v>2.4192</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4171</v>
+        <v>4.7626</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5544</v>
+        <v>2.4941</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1373</v>
+        <v>2.2685</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1003</v>
+        <v>0.3036</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7927</v>
+        <v>0.1528</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6924</v>
+        <v>0.1507</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.6237</v>
+        <v>-3.7112</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5515</v>
+        <v>3.0154</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1261</v>
+        <v>-2.0946</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4762</v>
+        <v>-0.6877</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3501</v>
+        <v>-1.4068</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5361</v>
+        <v>0.9304</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5361</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. BRYANT</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4272</v>
+        <v>2.0803</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3078</v>
+        <v>0.55</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1194</v>
+        <v>1.5303</v>
       </c>
       <c r="G5" t="n">
-        <v>5.0661</v>
+        <v>2.5174</v>
       </c>
       <c r="H5" t="n">
-        <v>2.6469</v>
+        <v>3.347</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4192</v>
+        <v>-0.8297</v>
       </c>
       <c r="J5" t="n">
-        <v>4.7626</v>
+        <v>2.4171</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4941</v>
+        <v>2.5544</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2685</v>
+        <v>-0.1373</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3036</v>
+        <v>0.1003</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1528</v>
+        <v>0.7927</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1507</v>
+        <v>-0.6924</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.7112</v>
+        <v>-1.6237</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0154</v>
+        <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.8735</v>
+        <v>-0.8287</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0297</v>
+        <v>-0.2434</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.8437</v>
+        <v>-0.5854</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9304</v>
+        <v>-0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3558</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1811</v>
+        <v>-0.0631</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6686</v>
+        <v>-0.5507</v>
       </c>
       <c r="F6" t="n">
         <v>0.4876</v>
@@ -922,10 +922,10 @@
         <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0747</v>
+        <v>0.1926</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U6" t="n">
         <v>0.3734</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.67</v>
+        <v>-0.2758</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6556</v>
+        <v>-1.4629</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9855</v>
+        <v>1.1872</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7092</v>
@@ -1000,13 +1000,13 @@
         <v>2.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5639</v>
+        <v>-1.1696</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8883</v>
+        <v>-0.6956</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6756</v>
+        <v>-0.474</v>
       </c>
       <c r="V7" t="n">
         <v>0.2836</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0087</v>
+        <v>-0.7489</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8046</v>
+        <v>-0.612</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2041</v>
+        <v>-0.1369</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0535</v>
@@ -1078,13 +1078,13 @@
         <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0448</v>
+        <v>0.3047</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4481</v>
+        <v>-0.2555</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4929</v>
+        <v>0.5601</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4396</v>
+        <v>-2.4748</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.9468</v>
+        <v>-4.6795</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5071</v>
+        <v>2.2047</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1828</v>
@@ -1156,13 +1156,13 @@
         <v>3.4793</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4914</v>
+        <v>-1.5266</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1044</v>
+        <v>-0.8371</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.387</v>
+        <v>-0.6895</v>
       </c>
       <c r="V9" t="n">
         <v>1.4665</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2453</v>
+        <v>-2.9183</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2561</v>
+        <v>-2.0635</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9892</v>
+        <v>-0.8548</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1752</v>
@@ -1234,13 +1234,13 @@
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0896</v>
+        <v>0.4167</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2829</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3725</v>
+        <v>0.507</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>11.7328</v>
+        <v>12.8529</v>
       </c>
       <c r="E11" t="n">
-        <v>3.372100000000001</v>
+        <v>4.4923</v>
       </c>
       <c r="F11" t="n">
-        <v>8.3605</v>
+        <v>8.360700000000001</v>
       </c>
       <c r="G11" t="n">
         <v>13.3698</v>
@@ -1312,10 +1312,10 @@
         <v>18.5564</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.49</v>
+        <v>-6.369800000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.4034</v>
+        <v>-4.2832</v>
       </c>
       <c r="U11" t="n">
         <v>-2.0866</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.017</v>
+        <v>4.4324</v>
       </c>
       <c r="E12" t="n">
         <v>2.7726</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2444</v>
+        <v>1.6598</v>
       </c>
       <c r="G12" t="n">
         <v>2.4755</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6137</v>
+        <v>1.0291</v>
       </c>
       <c r="T12" t="n">
         <v>-0.0351</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6489</v>
+        <v>1.0642</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6859</v>
+        <v>1.7429</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7452</v>
+        <v>3.3118</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0593</v>
+        <v>-1.5689</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1466</v>
+        <v>1.737</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7756</v>
+        <v>1.1548</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.629</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>3.0312</v>
+        <v>3.5673</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1846</v>
+        <v>2.3527</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8465</v>
+        <v>1.2146</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.8845</v>
+        <v>-1.8303</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4091</v>
+        <v>-1.1979</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.4755</v>
+        <v>-0.6323</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.9432</v>
+        <v>0.232</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.0307</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0876</v>
+        <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>4.552</v>
+        <v>-0.226</v>
       </c>
       <c r="T13" t="n">
-        <v>3.6725</v>
+        <v>-0.2555</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.0294</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9304</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4005</v>
+        <v>0.1121</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1939</v>
+        <v>-0.4831</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7933</v>
+        <v>0.5952</v>
       </c>
       <c r="G14" t="n">
-        <v>1.737</v>
+        <v>-0.2168</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1548</v>
+        <v>-0.4645</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.2477</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5673</v>
+        <v>0.2515</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3527</v>
+        <v>0.1043</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2146</v>
+        <v>0.1472</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8303</v>
+        <v>-0.4683</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1979</v>
+        <v>-0.5688</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6323</v>
+        <v>0.1005</v>
       </c>
       <c r="P14" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5685</v>
+        <v>1.3289</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3734</v>
+        <v>0.2833</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.195</v>
+        <v>1.0455</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>A. M'BAYE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8655</v>
+        <v>-0.2325</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6964</v>
+        <v>1.3923</v>
       </c>
       <c r="F15" t="n">
-        <v>0.169</v>
+        <v>-1.6249</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2168</v>
+        <v>-1.4985</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4645</v>
+        <v>-1.378</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2477</v>
+        <v>-0.1205</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2515</v>
+        <v>0.489</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1043</v>
+        <v>0.1344</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1472</v>
+        <v>0.3546</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4683</v>
+        <v>-1.9875</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5688</v>
+        <v>-1.5124</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1005</v>
+        <v>-0.4751</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0823</v>
+        <v>-0.0382</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4629</v>
+        <v>-0.1689</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6194</v>
+        <v>0.1307</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5806</v>
+        <v>-0.6407</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.9427</v>
+        <v>-2.5889</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3621</v>
+        <v>1.9481</v>
       </c>
       <c r="G16" t="n">
         <v>-2.2987</v>
@@ -1702,13 +1702,13 @@
         <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2542</v>
+        <v>1.194</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5975</v>
+        <v>-0.2436</v>
       </c>
       <c r="U16" t="n">
-        <v>1.8517</v>
+        <v>1.4376</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. M'BAYE</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9345</v>
+        <v>-0.8963</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0385</v>
+        <v>-0.6139</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.973</v>
+        <v>-0.2825</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4985</v>
+        <v>0.1466</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.378</v>
+        <v>0.7756</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1205</v>
+        <v>-0.629</v>
       </c>
       <c r="J17" t="n">
-        <v>0.489</v>
+        <v>3.0312</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1344</v>
+        <v>2.1846</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3546</v>
+        <v>0.8465</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9875</v>
+        <v>-2.8845</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5124</v>
+        <v>-1.4091</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4751</v>
+        <v>-1.4755</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>-3.9432</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-6.0307</v>
       </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7402</v>
+        <v>1.9698</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5228</v>
+        <v>1.3135</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2175</v>
+        <v>0.6563</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0722</v>
+        <v>0.9304</v>
       </c>
       <c r="W17" t="n">
         <v>1.0722</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5638</v>
+        <v>-1.0879</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0402</v>
+        <v>-1.0697</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4764</v>
+        <v>-0.0182</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.0066</v>
+        <v>-0.2511</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.9364</v>
+        <v>-0.358</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0702</v>
+        <v>0.1069</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7627</v>
+        <v>1.8152</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.5356</v>
+        <v>1.0727</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7729</v>
+        <v>0.7425</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2439</v>
+        <v>-2.0663</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4008</v>
+        <v>-1.4306</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8431</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>-3.4793</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.3917</v>
+        <v>-4.639</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0211</v>
+        <v>1.0341</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1142</v>
+        <v>0.1458</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1353</v>
+        <v>0.8883</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1415</v>
+        <v>-1.177</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7319</v>
+        <v>-1.9222</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5905</v>
+        <v>0.7452</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.4689</v>
+        <v>-2.0066</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3336</v>
+        <v>-1.9364</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.1353</v>
+        <v>-0.0702</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.5395</v>
+        <v>-0.7627</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0672</v>
+        <v>-1.5356</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.6067</v>
+        <v>0.7729</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9294</v>
+        <v>-1.2439</v>
       </c>
       <c r="N19" t="n">
         <v>-0.4008</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5286</v>
+        <v>-0.8431</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4718</v>
+        <v>0.3657</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0395</v>
+        <v>0.2322</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4323</v>
+        <v>0.1336</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9945</v>
+        <v>-2.0235</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4165</v>
+        <v>-2.614</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.578</v>
+        <v>0.5905</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.2098</v>
+        <v>-3.4689</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.5366</v>
+        <v>-0.3336</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.6732</v>
+        <v>-3.1353</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.9767</v>
+        <v>-2.5395</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.9893</v>
+        <v>0.0672</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9873</v>
+        <v>-2.6067</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2331</v>
+        <v>-0.9294</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5473</v>
+        <v>-0.4008</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6859</v>
+        <v>-0.5286</v>
       </c>
       <c r="P20" t="n">
         <v>1.3917</v>
@@ -2014,28 +2014,28 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2179</v>
+        <v>0.5898</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1142</v>
+        <v>0.1575</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1037</v>
+        <v>0.4323</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3943</v>
+        <v>-0.5361</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0867</v>
+        <v>-2.6521</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4851</v>
+        <v>-2.2986</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6016</v>
+        <v>-0.3535</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2511</v>
+        <v>-4.2098</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.358</v>
+        <v>-2.5366</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1069</v>
+        <v>-1.6732</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8152</v>
+        <v>-2.9767</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0727</v>
+        <v>-1.9893</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7425</v>
+        <v>-0.9873</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0663</v>
+        <v>-1.2331</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4306</v>
+        <v>-0.5473</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.6859</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.4793</v>
+        <v>1.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.639</v>
+        <v>-0.232</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9647</v>
+        <v>0.5603</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2696</v>
+        <v>0.2322</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3049</v>
+        <v>0.3282</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6083</v>
+        <v>-0.3943</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6083</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. STEVENS</t>
+          <t>J. RHODEN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1379</v>
+        <v>-3.4479</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9052</v>
+        <v>-0.8376</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2327</v>
+        <v>-2.6104</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1206</v>
+        <v>-2.6581</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4347</v>
+        <v>-2.8955</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6859</v>
+        <v>0.2374</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2414</v>
+        <v>0.2982</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1912</v>
+        <v>-0.6785</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0502</v>
+        <v>0.9768</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8791</v>
+        <v>-2.9564</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2435</v>
+        <v>-2.217</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.5515</v>
+        <v>0.6959</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4793</v>
+        <v>-1.3917</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7481</v>
+        <v>0.6587</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1845</v>
+        <v>0.2559</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9326</v>
+        <v>0.4028</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.214</v>
+        <v>-2.1444</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.214</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. RHODEN</t>
+          <t>L. STEVENS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2622</v>
+        <v>-3.5031</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4273</v>
+        <v>-3.5514</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8348</v>
+        <v>0.0483</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.6581</v>
+        <v>-1.1206</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8955</v>
+        <v>-0.4347</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2374</v>
+        <v>-0.6859</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2982</v>
+        <v>-0.2414</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6785</v>
+        <v>-0.1912</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9768</v>
+        <v>-0.0502</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.9564</v>
+        <v>-0.8791</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.217</v>
+        <v>-0.2435</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6959</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.3917</v>
+        <v>-3.4793</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1555</v>
+        <v>1.3829</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3339</v>
+        <v>0.1693</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1784</v>
+        <v>1.2136</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1444</v>
+        <v>-1.214</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1444</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-11.7328</v>
+        <v>-9.3736</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.502299999999998</v>
+        <v>-8.502700000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.2303</v>
+        <v>-0.8713</v>
       </c>
       <c r="G24" t="n">
         <v>-13.37</v>
@@ -2299,7 +2299,7 @@
         <v>-2.0916</v>
       </c>
       <c r="J24" t="n">
-        <v>3.3946</v>
+        <v>3.394599999999999</v>
       </c>
       <c r="K24" t="n">
         <v>-1.3888</v>
@@ -2317,7 +2317,7 @@
         <v>-6.875</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.639</v>
+        <v>-4.638999999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-18.5562</v>
@@ -2326,13 +2326,13 @@
         <v>13.9174</v>
       </c>
       <c r="S24" t="n">
-        <v>7.489999999999999</v>
+        <v>9.8491</v>
       </c>
       <c r="T24" t="n">
-        <v>2.0865</v>
+        <v>2.0866</v>
       </c>
       <c r="U24" t="n">
-        <v>5.4036</v>
+        <v>7.762499999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-1.214</v>
